--- a/przyklady/wynik/Raport_wnioski_2026-08-22_09-00.xlsx
+++ b/przyklady/wynik/Raport_wnioski_2026-08-22_09-00.xlsx
@@ -37,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,37 +45,20 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -448,19 +431,10 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="7" customWidth="1" min="11" max="11"/>
-    <col width="7" customWidth="1" min="12" max="12"/>
-    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="31.42857142857143" customWidth="1" min="1" max="1"/>
+    <col width="28.57142857142857" customWidth="1" min="2" max="2"/>
+    <col width="37.14285714285715" customWidth="1" min="3" max="3"/>
+    <col width="74.28571428571429" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,7 +448,7 @@
           <t>Uczeń</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -496,12 +470,12 @@
           <t>Brzozowska Anna</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>utworzono — moduł VII, wpisanych ocen: 11</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr"/>
+      <c r="D2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -514,12 +488,12 @@
           <t>Dąbrowski Marcel</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>utworzono — moduł VII, wpisanych ocen: 10</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr"/>
+      <c r="D3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -532,7 +506,7 @@
           <t>Kwiatkowska Zofia</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>utworzono — moduł VII, wpisanych ocen: 11</t>
         </is>
@@ -554,7 +528,7 @@
           <t>Lis Bartosz</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>utworzono — moduł VII, wpisanych ocen: 9</t>
         </is>
@@ -576,12 +550,12 @@
           <t>Nowicka Helena</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>utworzono — moduł VII, wpisanych ocen: 11</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -594,12 +568,12 @@
           <t>Wróbel Ignacy</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>utworzono — moduł VII, wpisanych ocen: 9</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
